--- a/DataDriven/Bantuan.xlsx
+++ b/DataDriven/Bantuan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/VScode/QA PPA Team (Android)/DataDriven/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aldopriamnistikogmail.com/Projects/Project_Automation_RobotFramework_StarAsiaPerkasa/DataDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E0A7E5-CA53-584C-9AFC-7DB1E37C8F62}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54564CE2-53DE-2D45-BB37-4F453265663C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" xr2:uid="{7193F10B-A1B6-884D-99BA-D3AD237142D9}"/>
+    <workbookView xWindow="1360" yWindow="660" windowWidth="28040" windowHeight="17180" xr2:uid="{7193F10B-A1B6-884D-99BA-D3AD237142D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Chat_Virtual</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Deskripsi</t>
   </si>
   <si>
-    <t>Testing Ini</t>
-  </si>
-  <si>
     <t>Screenshot</t>
   </si>
   <si>
@@ -64,6 +61,15 @@
   </si>
   <si>
     <t>Hapus Laporan</t>
+  </si>
+  <si>
+    <t>judul_Beri_Masukan</t>
+  </si>
+  <si>
+    <t>INI TESTING COY</t>
+  </si>
+  <si>
+    <t>Testing Inisjdasdjajsdajdslkj</t>
   </si>
 </sst>
 </file>
@@ -415,10 +421,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A154B944-1684-AE45-95DF-1459A3AA47E3}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,13 +438,16 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -449,13 +458,16 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
